--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/NEBRASKA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/NEBRASKA_2014.xlsx
@@ -679,7 +679,7 @@
         <v>35</v>
       </c>
       <c r="D18">
-        <v>0.009011328527291</v>
+        <v>0.009011328527291002</v>
       </c>
     </row>
     <row r="19">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C102">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C166">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C172">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C643">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C694">
